--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table63.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table63.xlsx
@@ -427,8 +427,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -519,7 +519,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
@@ -535,13 +535,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
@@ -549,17 +549,17 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 43" xfId="2"/>
@@ -1057,7 +1057,7 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
@@ -1068,30 +1068,30 @@
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="26" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="28"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="6" t="s">
         <v>5</v>
       </c>
